--- a/Excel/WeaponConfig.xlsx
+++ b/Excel/WeaponConfig.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="75">
   <si>
     <t>#</t>
   </si>
@@ -227,6 +227,36 @@
   </si>
   <si>
     <t>需要珍宝道尊之剑</t>
+  </si>
+  <si>
+    <t>冰霜之甲</t>
+  </si>
+  <si>
+    <t>1,2,3,1001</t>
+  </si>
+  <si>
+    <t>2001,10001</t>
+  </si>
+  <si>
+    <t>5,1</t>
+  </si>
+  <si>
+    <t>需要珍宝冰霜之甲</t>
+  </si>
+  <si>
+    <t>冰霜之戒</t>
+  </si>
+  <si>
+    <t>Bag/Equip/Box_Equip_1_5</t>
+  </si>
+  <si>
+    <t>1,2,3,1002</t>
+  </si>
+  <si>
+    <t>2002,10002</t>
+  </si>
+  <si>
+    <t>需要珍宝冰霜之戒</t>
   </si>
 </sst>
 </file>
@@ -1743,18 +1773,45 @@
       <c r="XES13" s="1"/>
     </row>
     <row r="14" s="2" customFormat="1" customHeight="1" spans="1:16 16366:16373">
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="4"/>
-      <c r="I14" s="1"/>
-      <c r="J14" s="1"/>
-      <c r="K14" s="1"/>
-      <c r="L14" s="1"/>
-      <c r="M14" s="1"/>
-      <c r="N14" s="1"/>
+      <c r="C14" s="1">
+        <v>9</v>
+      </c>
+      <c r="D14" s="1">
+        <v>9</v>
+      </c>
+      <c r="E14" s="1">
+        <v>0</v>
+      </c>
+      <c r="F14" s="1">
+        <v>1</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="I14" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="J14" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="K14" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="L14" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="M14" s="1">
+        <v>4</v>
+      </c>
+      <c r="N14" s="1">
+        <v>30000</v>
+      </c>
+      <c r="P14" s="1" t="s">
+        <v>69</v>
+      </c>
       <c r="XEL14" s="1"/>
       <c r="XEM14" s="1"/>
       <c r="XEN14" s="1"/>
@@ -1765,18 +1822,45 @@
       <c r="XES14" s="1"/>
     </row>
     <row r="15" s="2" customFormat="1" customHeight="1" spans="1:16 16366:16373">
-      <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="4"/>
-      <c r="I15" s="1"/>
-      <c r="J15" s="1"/>
-      <c r="K15" s="1"/>
-      <c r="L15" s="1"/>
-      <c r="M15" s="1"/>
-      <c r="N15" s="1"/>
+      <c r="C15" s="1">
+        <v>10</v>
+      </c>
+      <c r="D15" s="1">
+        <v>10</v>
+      </c>
+      <c r="E15" s="1">
+        <v>0</v>
+      </c>
+      <c r="F15" s="1">
+        <v>1</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="I15" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="J15" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="K15" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="L15" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="M15" s="1">
+        <v>4</v>
+      </c>
+      <c r="N15" s="1">
+        <v>30000</v>
+      </c>
+      <c r="P15" s="1" t="s">
+        <v>74</v>
+      </c>
       <c r="XEL15" s="1"/>
       <c r="XEM15" s="1"/>
       <c r="XEN15" s="1"/>

--- a/Excel/WeaponConfig.xlsx
+++ b/Excel/WeaponConfig.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="74">
   <si>
     <t>#</t>
   </si>
@@ -235,10 +235,7 @@
     <t>1,2,3,1001</t>
   </si>
   <si>
-    <t>2001,10001</t>
-  </si>
-  <si>
-    <t>5,1</t>
+    <t>28,10001</t>
   </si>
   <si>
     <t>需要珍宝冰霜之甲</t>
@@ -253,7 +250,7 @@
     <t>1,2,3,1002</t>
   </si>
   <si>
-    <t>2002,10002</t>
+    <t>28,10002</t>
   </si>
   <si>
     <t>需要珍宝冰霜之戒</t>
@@ -1801,7 +1798,7 @@
         <v>67</v>
       </c>
       <c r="L14" s="7" t="s">
-        <v>68</v>
+        <v>23</v>
       </c>
       <c r="M14" s="1">
         <v>4</v>
@@ -1810,7 +1807,7 @@
         <v>30000</v>
       </c>
       <c r="P14" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="XEL14" s="1"/>
       <c r="XEM14" s="1"/>
@@ -1835,22 +1832,22 @@
         <v>1</v>
       </c>
       <c r="G15" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="H15" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="H15" s="1" t="s">
+      <c r="I15" s="7" t="s">
         <v>71</v>
-      </c>
-      <c r="I15" s="7" t="s">
-        <v>72</v>
       </c>
       <c r="J15" s="7" t="s">
         <v>52</v>
       </c>
       <c r="K15" s="7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="L15" s="7" t="s">
-        <v>68</v>
+        <v>23</v>
       </c>
       <c r="M15" s="1">
         <v>4</v>
@@ -1859,7 +1856,7 @@
         <v>30000</v>
       </c>
       <c r="P15" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="XEL15" s="1"/>
       <c r="XEM15" s="1"/>

--- a/Excel/WeaponConfig.xlsx
+++ b/Excel/WeaponConfig.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="75">
   <si>
     <t>#</t>
   </si>
@@ -91,7 +91,7 @@
     <t>归元链</t>
   </si>
   <si>
-    <t>Bag/Equip/Box_Equip_1_3</t>
+    <t>Bag/Equip/Box_Equip_4_3</t>
   </si>
   <si>
     <t>1,2,3</t>
@@ -115,7 +115,7 @@
     <t>天蚕甲</t>
   </si>
   <si>
-    <t>Bag/Equip/Box_Equip_1_2</t>
+    <t>Bag/Equip/Box_Equip_4_2</t>
   </si>
   <si>
     <t>1500,150,150</t>
@@ -133,60 +133,63 @@
     <t>惊鸿剑</t>
   </si>
   <si>
+    <t>Bag/Equip/Box_Equip_4_1</t>
+  </si>
+  <si>
+    <t>2000,200,200</t>
+  </si>
+  <si>
+    <t>1003,2003</t>
+  </si>
+  <si>
+    <t>攻击</t>
+  </si>
+  <si>
+    <t>看广告{0}个</t>
+  </si>
+  <si>
+    <t>飞影追魂卷</t>
+  </si>
+  <si>
+    <t>Store/Store5002</t>
+  </si>
+  <si>
+    <t>4000,400,400</t>
+  </si>
+  <si>
+    <t>10003,10</t>
+  </si>
+  <si>
+    <t>2,3</t>
+  </si>
+  <si>
+    <t>cd</t>
+  </si>
+  <si>
+    <t>需要道具飞影追魂卷</t>
+  </si>
+  <si>
+    <t>流光逐影印</t>
+  </si>
+  <si>
+    <t>Store/Store5004</t>
+  </si>
+  <si>
+    <t>10003,11</t>
+  </si>
+  <si>
+    <t>攻速</t>
+  </si>
+  <si>
+    <t>需要道具流光逐影印</t>
+  </si>
+  <si>
+    <t>圣战之刃</t>
+  </si>
+  <si>
     <t>Bag/Equip/Box_Equip_1_1</t>
   </si>
   <si>
-    <t>2000,200,200</t>
-  </si>
-  <si>
-    <t>1003,2003</t>
-  </si>
-  <si>
-    <t>攻击</t>
-  </si>
-  <si>
-    <t>看广告{0}个</t>
-  </si>
-  <si>
-    <t>飞影追魂卷</t>
-  </si>
-  <si>
-    <t>Store/Store5002</t>
-  </si>
-  <si>
-    <t>4000,400,400</t>
-  </si>
-  <si>
-    <t>10003,10</t>
-  </si>
-  <si>
-    <t>2,3</t>
-  </si>
-  <si>
-    <t>cd</t>
-  </si>
-  <si>
-    <t>需要道具飞影追魂卷</t>
-  </si>
-  <si>
-    <t>流光逐影印</t>
-  </si>
-  <si>
-    <t>Store/Store5004</t>
-  </si>
-  <si>
-    <t>10003,11</t>
-  </si>
-  <si>
-    <t>攻速</t>
-  </si>
-  <si>
-    <t>需要道具流光逐影印</t>
-  </si>
-  <si>
-    <t>圣战之刃</t>
-  </si>
-  <si>
     <t>1,2,3,1004</t>
   </si>
   <si>
@@ -244,7 +247,7 @@
     <t>冰霜之戒</t>
   </si>
   <si>
-    <t>Bag/Equip/Box_Equip_1_5</t>
+    <t>Bag/Equip/Box_Equip_4_7</t>
   </si>
   <si>
     <t>1,2,3,1002</t>
@@ -1635,16 +1638,16 @@
         <v>50</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K11" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L11" s="7" t="s">
         <v>23</v>
@@ -1657,7 +1660,7 @@
       </c>
       <c r="O11" s="2"/>
       <c r="P11" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="XEL11" s="1"/>
       <c r="XEM11" s="1"/>
@@ -1684,19 +1687,19 @@
         <v>1</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I12" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K12" s="7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L12" s="7" t="s">
         <v>23</v>
@@ -1709,7 +1712,7 @@
       </c>
       <c r="O12" s="2"/>
       <c r="P12" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="XEL12" s="1"/>
       <c r="XEM12" s="1"/>
@@ -1734,19 +1737,19 @@
         <v>1</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I13" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K13" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="L13" s="7" t="s">
         <v>23</v>
@@ -1758,7 +1761,7 @@
         <v>20000</v>
       </c>
       <c r="P13" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="XEL13" s="1"/>
       <c r="XEM13" s="1"/>
@@ -1783,19 +1786,19 @@
         <v>1</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H14" s="1" t="s">
         <v>27</v>
       </c>
       <c r="I14" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K14" s="7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L14" s="7" t="s">
         <v>23</v>
@@ -1807,7 +1810,7 @@
         <v>30000</v>
       </c>
       <c r="P14" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="XEL14" s="1"/>
       <c r="XEM14" s="1"/>
@@ -1832,19 +1835,19 @@
         <v>1</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I15" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K15" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="L15" s="7" t="s">
         <v>23</v>
@@ -1856,7 +1859,7 @@
         <v>30000</v>
       </c>
       <c r="P15" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="XEL15" s="1"/>
       <c r="XEM15" s="1"/>
